--- a/Inventor_BOM_Raw_Procurement.xlsx
+++ b/Inventor_BOM_Raw_Procurement.xlsx
@@ -637,13 +637,13 @@
     <t>Automatic Tea Steeping mechanism</t>
   </si>
   <si>
-    <t>Frabricate - 1st round</t>
+    <t>Fabricate - 1st round</t>
   </si>
   <si>
     <t>Buy</t>
   </si>
   <si>
-    <t>Frabricate - 2nd round</t>
+    <t>Fabricate - 2nd round</t>
   </si>
 </sst>
 </file>
